--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104648_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104648_W22.xlsx
@@ -565,58 +565,58 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.0408</v>
+        <v>10.1644</v>
       </c>
       <c r="E2" t="n">
-        <v>10.3916</v>
+        <v>10.4165</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3508</v>
+        <v>-0.252</v>
       </c>
       <c r="G2" t="n">
-        <v>8.3749</v>
+        <v>8.3597</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4184</v>
+        <v>0.4193</v>
       </c>
       <c r="I2" t="n">
-        <v>7.9565</v>
+        <v>7.9404</v>
       </c>
       <c r="J2" t="n">
-        <v>11.7132</v>
+        <v>11.6711</v>
       </c>
       <c r="K2" t="n">
-        <v>2.0882</v>
+        <v>2.0717</v>
       </c>
       <c r="L2" t="n">
-        <v>9.625</v>
+        <v>9.599399999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>-3.3383</v>
+        <v>-3.3114</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.6698</v>
+        <v>-1.6524</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.6685</v>
+        <v>-1.659</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S2" t="n">
-        <v>0.078</v>
+        <v>0.2113</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1875</v>
+        <v>-0.1165</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2655</v>
+        <v>0.3278</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.267</v>
+        <v>6.1443</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3097</v>
+        <v>4.6642</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9572</v>
+        <v>1.4801</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6419</v>
+        <v>3.6496</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8255</v>
+        <v>-0.8162</v>
       </c>
       <c r="I3" t="n">
-        <v>4.4674</v>
+        <v>4.4658</v>
       </c>
       <c r="J3" t="n">
-        <v>4.4326</v>
+        <v>4.4229</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L3" t="n">
-        <v>4.3287</v>
+        <v>4.3195</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7907999999999999</v>
+        <v>-0.7733</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.9294</v>
+        <v>-0.9196</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S3" t="n">
-        <v>1.8104</v>
+        <v>0.6736</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8771</v>
+        <v>0.2413</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9333</v>
+        <v>0.4324</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3533</v>
+        <v>5.7605</v>
       </c>
       <c r="E4" t="n">
-        <v>5.2184</v>
+        <v>5.7862</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1349</v>
+        <v>-0.0257</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9402</v>
+        <v>1.9428</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1704</v>
+        <v>-1.1581</v>
       </c>
       <c r="I4" t="n">
-        <v>3.1106</v>
+        <v>3.101</v>
       </c>
       <c r="J4" t="n">
-        <v>3.9967</v>
+        <v>3.978</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1212</v>
+        <v>0.1207</v>
       </c>
       <c r="L4" t="n">
-        <v>3.8755</v>
+        <v>3.8573</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0566</v>
+        <v>-2.0351</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1863</v>
+        <v>0.59</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4174</v>
+        <v>0.174</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6037</v>
+        <v>0.416</v>
       </c>
       <c r="V4" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W4" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. SULEJMANOVIC</t>
+          <t>C. AUDIGE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.7657</v>
+        <v>2.6876</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5729</v>
+        <v>2.473</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1928</v>
+        <v>0.2145</v>
       </c>
       <c r="G5" t="n">
-        <v>2.2081</v>
+        <v>1.3533</v>
       </c>
       <c r="H5" t="n">
-        <v>0.241</v>
+        <v>1.6203</v>
       </c>
       <c r="I5" t="n">
-        <v>1.9671</v>
+        <v>-0.267</v>
       </c>
       <c r="J5" t="n">
-        <v>3.7342</v>
+        <v>3.0738</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6899</v>
+        <v>3.5885</v>
       </c>
       <c r="L5" t="n">
-        <v>2.0443</v>
+        <v>-0.5148</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5261</v>
+        <v>-1.7205</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4489</v>
+        <v>-1.9683</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0772</v>
+        <v>0.2477</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="Q5" t="n">
-        <v>-3.4025</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4952</v>
+        <v>2.7316</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4649</v>
+        <v>0.2856</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2411</v>
+        <v>-0.0073</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2238</v>
+        <v>0.2929</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.5447</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>C. AUDIGE</t>
+          <t>E. SULEJMANOVIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6188</v>
+        <v>2.172</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6936</v>
+        <v>0.9497</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0747</v>
+        <v>1.2224</v>
       </c>
       <c r="G6" t="n">
-        <v>1.3691</v>
+        <v>2.1954</v>
       </c>
       <c r="H6" t="n">
-        <v>1.6278</v>
+        <v>0.2385</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2586</v>
+        <v>1.9569</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1162</v>
+        <v>3.7003</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6121</v>
+        <v>1.6752</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4959</v>
+        <v>2.025</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.747</v>
+        <v>-1.5048</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.9843</v>
+        <v>-1.4367</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2373</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>1.5878</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-3.4145</v>
       </c>
       <c r="R6" t="n">
-        <v>2.722</v>
+        <v>2.5039</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7917999999999999</v>
+        <v>0.8871</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8347</v>
+        <v>0.6639</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0429</v>
+        <v>0.2232</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.366</v>
+        <v>2.112</v>
       </c>
       <c r="E7" t="n">
-        <v>1.774</v>
+        <v>2.3713</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4079</v>
+        <v>-0.2593</v>
       </c>
       <c r="G7" t="n">
-        <v>0.973</v>
+        <v>0.9751</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8397</v>
+        <v>0.8441</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1333</v>
+        <v>0.131</v>
       </c>
       <c r="J7" t="n">
-        <v>2.6087</v>
+        <v>2.5946</v>
       </c>
       <c r="K7" t="n">
-        <v>1.4546</v>
+        <v>1.4479</v>
       </c>
       <c r="L7" t="n">
-        <v>1.1541</v>
+        <v>1.1467</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.6357</v>
+        <v>-1.6194</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6149</v>
+        <v>-0.6037</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.0209</v>
+        <v>-1.0157</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8753</v>
+        <v>-0.1394</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8347</v>
+        <v>-0.2232</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0405</v>
+        <v>0.0838</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5092</v>
+        <v>1.1939</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1776</v>
+        <v>0.2252</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6868</v>
+        <v>0.9687</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.5348</v>
+        <v>-1.53</v>
       </c>
       <c r="H8" t="n">
-        <v>-2.5771</v>
+        <v>-2.579</v>
       </c>
       <c r="I8" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3659</v>
+        <v>-0.3831</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.1123</v>
+        <v>-1.1279</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7463</v>
+        <v>0.7447</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1689</v>
+        <v>-1.1469</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4648</v>
+        <v>-1.4511</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.1881</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9043</v>
+        <v>-0.4811</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0429</v>
+        <v>0.2929</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3176</v>
+        <v>1.3187</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2249</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="9">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1648</v>
+        <v>0.375</v>
       </c>
       <c r="E9" t="n">
-        <v>1.7614</v>
+        <v>2.0848</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9262</v>
+        <v>-1.7098</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4189</v>
+        <v>-1.4205</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.1661</v>
+        <v>-0.1584</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.2529</v>
+        <v>-1.2621</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3594</v>
+        <v>2.3358</v>
       </c>
       <c r="K9" t="n">
-        <v>1.4719</v>
+        <v>1.4651</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8875</v>
+        <v>0.8707</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.7783</v>
+        <v>-3.7563</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.638</v>
+        <v>-1.6235</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1404</v>
+        <v>-2.1328</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.7458</v>
+        <v>-0.2045</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5565</v>
+        <v>-0.2023</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1893</v>
+        <v>-0.0022</v>
       </c>
       <c r="V9" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. WEBB III</t>
+          <t>K. TILLIE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.2449</v>
+        <v>-1.5446</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8993</v>
+        <v>-2.9214</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6544</v>
+        <v>1.3768</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.8315</v>
+        <v>-1.2661</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1037</v>
+        <v>-1.2494</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7277</v>
+        <v>-0.0166</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3689</v>
+        <v>-0.9795</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.662</v>
+        <v>-0.7035</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2931</v>
+        <v>-0.276</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.4626</v>
+        <v>-0.2866</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4417</v>
+        <v>-0.546</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.0209</v>
+        <v>0.2593</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4278</v>
+        <v>0.4727</v>
       </c>
       <c r="T10" t="n">
-        <v>0.738</v>
+        <v>0.3344</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6899</v>
+        <v>0.1383</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1607</v>
+        <v>0.387</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1607</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>K. TILLIE</t>
+          <t>J. WEBB III</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9798</v>
+        <v>-2.1681</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.3739</v>
+        <v>-2.5019</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3941</v>
+        <v>0.3338</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.2618</v>
+        <v>-1.8442</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2511</v>
+        <v>-1.1111</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0107</v>
+        <v>-0.7331</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.9664</v>
+        <v>-0.3972</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6998</v>
+        <v>-0.6797</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2666</v>
+        <v>0.2826</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.2954</v>
+        <v>-1.4471</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.5513</v>
+        <v>-0.4314</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2559</v>
+        <v>-1.0157</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.1342</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>1.5934</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0305</v>
+        <v>0.5168</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1391</v>
+        <v>0.1716</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1697</v>
+        <v>0.3452</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3856</v>
+        <v>-0.1578</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3856</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9542</v>
+        <v>-2.7959</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.1616</v>
+        <v>-1.0482</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.7925</v>
+        <v>-1.7477</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.5164</v>
+        <v>-1.5101</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.1357</v>
+        <v>-0.1323</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3807</v>
+        <v>-1.3778</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1812</v>
+        <v>0.1807</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L12" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6976</v>
+        <v>-1.6907</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.205</v>
+        <v>-0.2012</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.4927</v>
+        <v>-1.4895</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3451</v>
+        <v>-0.1963</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2087</v>
+        <v>-0.0907</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1364</v>
+        <v>-0.1057</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,58 +1423,58 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.1159</v>
+        <v>-3.9569</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.1239</v>
+        <v>-4.1486</v>
       </c>
       <c r="F13" t="n">
-        <v>0.008</v>
+        <v>0.1917</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.6123</v>
+        <v>-3.6304</v>
       </c>
       <c r="H13" t="n">
-        <v>-1.7198</v>
+        <v>-1.734</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8926</v>
+        <v>-1.8965</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.5985</v>
+        <v>-1.6374</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.0977</v>
+        <v>-0.1249</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.5008</v>
+        <v>-1.5125</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.0139</v>
+        <v>-1.9931</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.6221</v>
+        <v>-1.6091</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3918</v>
+        <v>-0.384</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2767</v>
+        <v>-0.0988</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2571</v>
+        <v>-0.2349</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0197</v>
+        <v>0.1361</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>19.4612</v>
+        <v>20.1442</v>
       </c>
       <c r="E14" t="n">
-        <v>17.9853</v>
+        <v>18.3508</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4761</v>
+        <v>1.7935</v>
       </c>
       <c r="G14" t="n">
-        <v>7.3315</v>
+        <v>7.274599999999998</v>
       </c>
       <c r="H14" t="n">
-        <v>-5.822500000000001</v>
+        <v>-5.8163</v>
       </c>
       <c r="I14" t="n">
-        <v>13.154</v>
+        <v>13.091</v>
       </c>
       <c r="J14" t="n">
-        <v>28.8425</v>
+        <v>28.56</v>
       </c>
       <c r="K14" t="n">
-        <v>8.039299999999999</v>
+        <v>7.905399999999998</v>
       </c>
       <c r="L14" t="n">
-        <v>20.8032</v>
+        <v>20.6543</v>
       </c>
       <c r="M14" t="n">
-        <v>-21.5112</v>
+        <v>-21.2852</v>
       </c>
       <c r="N14" t="n">
-        <v>-13.8619</v>
+        <v>-13.7218</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.649500000000001</v>
+        <v>-7.563500000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>7.939099999999999</v>
+        <v>7.967100000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-14.7442</v>
+        <v>-14.7962</v>
       </c>
       <c r="R14" t="n">
-        <v>22.6834</v>
+        <v>22.7633</v>
       </c>
       <c r="S14" t="n">
-        <v>2.1018</v>
+        <v>2.81</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4837999999999998</v>
+        <v>0.2292</v>
       </c>
       <c r="U14" t="n">
-        <v>2.5858</v>
+        <v>2.5807</v>
       </c>
       <c r="V14" t="n">
-        <v>2.088900000000001</v>
+        <v>2.092700000000001</v>
       </c>
       <c r="W14" t="n">
-        <v>4.3707</v>
+        <v>4.3579</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.2819</v>
+        <v>-2.2653</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2348</v>
+        <v>1.0737</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3968</v>
+        <v>1.7259</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.1619</v>
+        <v>-0.6522</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6356</v>
+        <v>1.6498</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0864</v>
+        <v>1.0939</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5492</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7316</v>
+        <v>3.7122</v>
       </c>
       <c r="K15" t="n">
-        <v>2.6148</v>
+        <v>2.6028</v>
       </c>
       <c r="L15" t="n">
-        <v>1.1168</v>
+        <v>1.1094</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.096</v>
+        <v>-2.0624</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.5284</v>
+        <v>-1.5089</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.5349</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9739</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="16">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0298</v>
+        <v>-0.1685</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3272</v>
+        <v>2.0753</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.2974</v>
+        <v>-2.2437</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.9861</v>
+        <v>-0.9826</v>
       </c>
       <c r="H16" t="n">
-        <v>0.6132</v>
+        <v>0.6173</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5993</v>
+        <v>-1.5999</v>
       </c>
       <c r="J16" t="n">
-        <v>2.0277</v>
+        <v>2.0105</v>
       </c>
       <c r="K16" t="n">
-        <v>1.2122</v>
+        <v>1.2066</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8156</v>
+        <v>0.8038999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>-3.0139</v>
+        <v>-2.9931</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.599</v>
+        <v>-0.5893</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.4149</v>
+        <v>-2.4037</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1183</v>
+        <v>-0.324</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2994</v>
+        <v>0.0648</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4177</v>
+        <v>-0.3888</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,40 +1735,40 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8509</v>
+        <v>-0.8215</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.8559</v>
+        <v>-0.8593</v>
       </c>
       <c r="F17" t="n">
-        <v>0.005</v>
+        <v>0.0378</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.8023</v>
+        <v>-0.8041</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9595</v>
+        <v>-0.962</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7864</v>
+        <v>-0.7896</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1732</v>
+        <v>-0.1724</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1573</v>
+        <v>0.1579</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0487</v>
+        <v>-0.0174</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0696</v>
+        <v>-0.0697</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0209</v>
+        <v>0.0523</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. KOUMADJE</t>
+          <t>J. RODRIGUEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8619</v>
+        <v>-1.2412</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3652</v>
+        <v>1.8565</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2271</v>
+        <v>-3.0977</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.6974</v>
+        <v>-0.5724</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0373</v>
+        <v>-0.1691</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.6601</v>
+        <v>-0.4033</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.4408</v>
+        <v>3.7811</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6274</v>
+        <v>0.7649</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1866</v>
+        <v>3.0162</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.2566</v>
+        <v>-4.3535</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4099</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.8467</v>
+        <v>-3.4194</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6805</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2268</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>0.9073</v>
+        <v>1.3658</v>
       </c>
       <c r="S18" t="n">
-        <v>1.9943</v>
+        <v>-0.07539999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>1.8721</v>
+        <v>0.0346</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1222</v>
+        <v>-0.11</v>
       </c>
       <c r="V18" t="n">
-        <v>0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. ROBINSON</t>
+          <t>D. STEPHENS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4352</v>
+        <v>-1.2572</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9725</v>
+        <v>0.2484</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4077</v>
+        <v>-1.5056</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6197</v>
+        <v>-2.1922</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1821</v>
+        <v>1.9128</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.8018</v>
+        <v>-4.105</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7345</v>
+        <v>0.5691000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>2.3164</v>
+        <v>1.9995</v>
       </c>
       <c r="L19" t="n">
-        <v>1.418</v>
+        <v>-1.4303</v>
       </c>
       <c r="M19" t="n">
-        <v>-4.3542</v>
+        <v>-2.7613</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1344</v>
+        <v>-0.0866</v>
       </c>
       <c r="O19" t="n">
-        <v>-3.2198</v>
+        <v>-2.6747</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.2683</v>
+        <v>1.1382</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.6293</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.361</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7458</v>
+        <v>-0.2031</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1603</v>
+        <v>-0.3207</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5855</v>
+        <v>0.1176</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7071</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5019</v>
+        <v>-1.3872</v>
       </c>
       <c r="E20" t="n">
-        <v>0.226</v>
+        <v>0.3009</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7279</v>
+        <v>-1.6881</v>
       </c>
       <c r="G20" t="n">
-        <v>2.0526</v>
+        <v>2.0551</v>
       </c>
       <c r="H20" t="n">
-        <v>1.0691</v>
+        <v>1.0766</v>
       </c>
       <c r="I20" t="n">
-        <v>0.9835</v>
+        <v>0.9785</v>
       </c>
       <c r="J20" t="n">
-        <v>3.4401</v>
+        <v>3.4136</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7317</v>
+        <v>1.7237</v>
       </c>
       <c r="L20" t="n">
-        <v>1.7085</v>
+        <v>1.6899</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3875</v>
+        <v>-1.3585</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6626</v>
+        <v>-0.6471</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7249</v>
+        <v>-0.7114</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.8147</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6472</v>
+        <v>-0.5318000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9043</v>
+        <v>-0.7877</v>
       </c>
       <c r="U20" t="n">
-        <v>0.2571</v>
+        <v>0.2559</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. STEPHENS</t>
+          <t>D. ROBINSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5344</v>
+        <v>-1.7583</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0288</v>
+        <v>0.8043</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.5632</v>
+        <v>-2.5626</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1995</v>
+        <v>-0.6258</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9134</v>
+        <v>1.1642</v>
       </c>
       <c r="I21" t="n">
-        <v>-4.1128</v>
+        <v>-1.79</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5853</v>
+        <v>3.7</v>
       </c>
       <c r="K21" t="n">
-        <v>2.0087</v>
+        <v>2.285</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.4234</v>
+        <v>1.415</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.7848</v>
+        <v>-4.3258</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0954</v>
+        <v>-1.1209</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.6894</v>
+        <v>-3.205</v>
       </c>
       <c r="P21" t="n">
-        <v>1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-3.6421</v>
       </c>
       <c r="R21" t="n">
-        <v>1.1342</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4691</v>
+        <v>0.4414</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5565</v>
+        <v>0.0439</v>
       </c>
       <c r="U21" t="n">
-        <v>0.08740000000000001</v>
+        <v>0.3975</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.7025</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ</t>
+          <t>C. KOUMADJE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.7346</v>
+        <v>-2.2798</v>
       </c>
       <c r="E22" t="n">
-        <v>1.2997</v>
+        <v>0.0492</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0343</v>
+        <v>-2.329</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.576</v>
+        <v>-3.6942</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.163</v>
+        <v>-1.0477</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4131</v>
+        <v>-2.6464</v>
       </c>
       <c r="J22" t="n">
-        <v>3.805</v>
+        <v>-0.4591</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7824</v>
+        <v>-0.6452</v>
       </c>
       <c r="L22" t="n">
-        <v>3.0227</v>
+        <v>0.1862</v>
       </c>
       <c r="M22" t="n">
-        <v>-4.381</v>
+        <v>-3.2351</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.9453</v>
+        <v>-0.4025</v>
       </c>
       <c r="O22" t="n">
-        <v>-3.4357</v>
+        <v>-2.8326</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.4952</v>
+        <v>-0.2276</v>
       </c>
       <c r="R22" t="n">
-        <v>1.361</v>
+        <v>0.9105</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5707</v>
+        <v>0.5737</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5565</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0142</v>
+        <v>-0.0044</v>
       </c>
       <c r="V22" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5463</v>
+        <v>0.1578</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.985</v>
+        <v>-2.2951</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6948</v>
+        <v>-1.5878</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.2902</v>
+        <v>-0.7073</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.4217</v>
+        <v>-1.4114</v>
       </c>
       <c r="H23" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.0974</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.514</v>
+        <v>-1.5087</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.0737</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6754</v>
+        <v>0.6722</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.749</v>
+        <v>-0.7524</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.348</v>
+        <v>-1.3312</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5831</v>
+        <v>-0.5749</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.7649</v>
+        <v>-0.7563</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0169</v>
+        <v>-0.339</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4869</v>
+        <v>-0.3695</v>
       </c>
       <c r="U23" t="n">
-        <v>0.47</v>
+        <v>0.0305</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B. DUBLJEVIC</t>
+          <t>S. YUSTA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.1952</v>
+        <v>-2.8239</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8106</v>
+        <v>-2.3964</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6153999999999999</v>
+        <v>-0.4275</v>
       </c>
       <c r="G24" t="n">
-        <v>0.2079</v>
+        <v>1.0263</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0159</v>
+        <v>0.6257</v>
       </c>
       <c r="I24" t="n">
-        <v>0.192</v>
+        <v>0.4006</v>
       </c>
       <c r="J24" t="n">
-        <v>0.2709</v>
+        <v>3.4611</v>
       </c>
       <c r="K24" t="n">
-        <v>0.159</v>
+        <v>2.2925</v>
       </c>
       <c r="L24" t="n">
-        <v>0.112</v>
+        <v>1.1686</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.063</v>
+        <v>-2.4348</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.1431</v>
+        <v>-1.6668</v>
       </c>
       <c r="O24" t="n">
-        <v>0.08</v>
+        <v>-0.768</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.2683</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.4025</v>
+        <v>-4.7803</v>
       </c>
       <c r="R24" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7972</v>
+        <v>-0.7316</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1603</v>
+        <v>-0.6902</v>
       </c>
       <c r="U24" t="n">
-        <v>0.6369</v>
+        <v>-0.0414</v>
       </c>
       <c r="V24" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.387</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>-0.387</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S. YUSTA</t>
+          <t>B. DUBLJEVIC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.4208</v>
+        <v>-2.8549</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.7034</v>
+        <v>-3.3121</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7175</v>
+        <v>0.4572</v>
       </c>
       <c r="G25" t="n">
-        <v>1.0199</v>
+        <v>0.216</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6175</v>
+        <v>0.0144</v>
       </c>
       <c r="I25" t="n">
-        <v>0.4025</v>
+        <v>0.2015</v>
       </c>
       <c r="J25" t="n">
-        <v>3.4891</v>
+        <v>0.2561</v>
       </c>
       <c r="K25" t="n">
-        <v>2.3031</v>
+        <v>0.1444</v>
       </c>
       <c r="L25" t="n">
-        <v>1.186</v>
+        <v>0.1117</v>
       </c>
       <c r="M25" t="n">
-        <v>-2.4692</v>
+        <v>-0.0402</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.6857</v>
+        <v>-0.13</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.7835</v>
+        <v>0.0898</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.722</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q25" t="n">
-        <v>-4.7635</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3332</v>
+        <v>0.1372</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0434</v>
+        <v>-0.3115</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2898</v>
+        <v>0.4487</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3856</v>
+        <v>-0.9317</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.3856</v>
+        <v>0.1578</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="26">
@@ -2437,58 +2437,58 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.2061</v>
+        <v>-3.6336</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.0275</v>
+        <v>-0.6984</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.1786</v>
+        <v>-2.9351</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.9448</v>
+        <v>-1.9391</v>
       </c>
       <c r="H26" t="n">
-        <v>1.3924</v>
+        <v>1.3929</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.3372</v>
+        <v>-3.332</v>
       </c>
       <c r="J26" t="n">
-        <v>1.7277</v>
+        <v>1.7105</v>
       </c>
       <c r="K26" t="n">
-        <v>1.4719</v>
+        <v>1.4651</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2558</v>
+        <v>0.2453</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.6725</v>
+        <v>-3.6496</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.593</v>
+        <v>-3.5774</v>
       </c>
       <c r="P26" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R26" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.9004</v>
+        <v>-0.3287</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4869</v>
+        <v>-0.1326</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.4134</v>
+        <v>-0.1961</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-19.4614</v>
+        <v>-19.4475</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.476</v>
+        <v>-1.793499999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-17.9854</v>
+        <v>-17.6538</v>
       </c>
       <c r="G27" t="n">
-        <v>-7.331499999999999</v>
+        <v>-7.2746</v>
       </c>
       <c r="H27" t="n">
-        <v>5.8225</v>
+        <v>5.8164</v>
       </c>
       <c r="I27" t="n">
-        <v>-13.1538</v>
+        <v>-13.0909</v>
       </c>
       <c r="J27" t="n">
-        <v>21.511</v>
+        <v>21.2853</v>
       </c>
       <c r="K27" t="n">
-        <v>13.8618</v>
+        <v>13.7219</v>
       </c>
       <c r="L27" t="n">
-        <v>7.6496</v>
+        <v>7.5635</v>
       </c>
       <c r="M27" t="n">
-        <v>-28.8426</v>
+        <v>-28.5599</v>
       </c>
       <c r="N27" t="n">
-        <v>-8.0396</v>
+        <v>-7.9056</v>
       </c>
       <c r="O27" t="n">
-        <v>-20.8031</v>
+        <v>-20.6543</v>
       </c>
       <c r="P27" t="n">
-        <v>-7.9391</v>
+        <v>-7.9671</v>
       </c>
       <c r="Q27" t="n">
-        <v>-22.6833</v>
+        <v>-22.7632</v>
       </c>
       <c r="R27" t="n">
-        <v>14.7442</v>
+        <v>14.7962</v>
       </c>
       <c r="S27" t="n">
-        <v>-2.1021</v>
+        <v>-2.1129</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.5859</v>
+        <v>-2.581</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4839</v>
+        <v>0.4680999999999999</v>
       </c>
       <c r="V27" t="n">
-        <v>-2.0888</v>
+        <v>-2.0926</v>
       </c>
       <c r="W27" t="n">
-        <v>2.281899999999999</v>
+        <v>2.2653</v>
       </c>
       <c r="X27" t="n">
-        <v>-4.3706</v>
+        <v>-4.3578</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104648_W22.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104648_W22.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>0</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-2.2653</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>0</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104648_W22.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-4.3578</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
